--- a/data/trans_orig/P16A04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268105</t>
+          <t>267985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246674</t>
+          <t>246680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257794</t>
+          <t>257721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519378</t>
+          <t>517848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530728</t>
+          <t>529851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480992</t>
+          <t>479589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491135</t>
+          <t>490947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478974</t>
+          <t>479470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495187</t>
+          <t>494428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965668</t>
+          <t>965172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983859</t>
+          <t>983403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313103</t>
+          <t>313467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327613</t>
+          <t>327501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644664</t>
+          <t>645542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653308</t>
+          <t>653313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345763</t>
+          <t>345389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355832</t>
+          <t>355824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350976</t>
+          <t>351539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364884</t>
+          <t>364872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702326</t>
+          <t>702356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718603</t>
+          <t>719064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199058</t>
+          <t>197831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195603</t>
+          <t>196612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205732</t>
+          <t>205758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397714</t>
+          <t>397393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408271</t>
+          <t>408187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261200</t>
+          <t>262164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269828</t>
+          <t>269804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263837</t>
+          <t>262992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275734</t>
+          <t>275720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530547</t>
+          <t>530803</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543569</t>
+          <t>543705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26383</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595397</t>
+          <t>595404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609507</t>
+          <t>609477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626178</t>
+          <t>624949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636182</t>
+          <t>636132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1226863</t>
+          <t>1226339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1243825</t>
+          <t>1243372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35696</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701622</t>
+          <t>702680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723373</t>
+          <t>723510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>753290</t>
+          <t>752850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>772083</t>
+          <t>772127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462122</t>
+          <t>1462458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490592</t>
+          <t>1490590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>75059</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112047</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>155307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3200957</t>
+          <t>3200466</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3229743</t>
+          <t>3230214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3285617</t>
+          <t>3285654</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3321131</t>
+          <t>3319925</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6496235</t>
+          <t>6499415</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6542675</t>
+          <t>6542531</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264211</t>
+          <t>263160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281439</t>
+          <t>281120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>251024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268723</t>
+          <t>269058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519678</t>
+          <t>520041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546109</t>
+          <t>546687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483361</t>
+          <t>484689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500751</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508817</t>
+          <t>508193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519632</t>
+          <t>519598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998740</t>
+          <t>998478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017936</t>
+          <t>1017746</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312409</t>
+          <t>312902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322099</t>
+          <t>322096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325769</t>
+          <t>325733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337169</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644325</t>
+          <t>644320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657292</t>
+          <t>657380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351022</t>
+          <t>351988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367534</t>
+          <t>368386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367833</t>
+          <t>367120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382223</t>
+          <t>382249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725583</t>
+          <t>726527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746990</t>
+          <t>747517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36417</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192052</t>
+          <t>191321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207844</t>
+          <t>207752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198018</t>
+          <t>198739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212642</t>
+          <t>212936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394794</t>
+          <t>397640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418143</t>
+          <t>418668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264556</t>
+          <t>264373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272997</t>
+          <t>273026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267388</t>
+          <t>268041</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278163</t>
+          <t>278182</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537460</t>
+          <t>537013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549482</t>
+          <t>550211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>36124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642660</t>
+          <t>642404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655756</t>
+          <t>655654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670917</t>
+          <t>671448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686622</t>
+          <t>686909</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1319026</t>
+          <t>1318326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340346</t>
+          <t>1339493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43263</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>74260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731206</t>
+          <t>733346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>756452</t>
+          <t>756799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>782771</t>
+          <t>781604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>804704</t>
+          <t>804574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1523559</t>
+          <t>1524232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1555229</t>
+          <t>1556595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73191</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118752</t>
+          <t>118937</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83466</t>
+          <t>80717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>124986</t>
+          <t>122792</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168636</t>
+          <t>168871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>229140</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3297351</t>
+          <t>3297166</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342912</t>
+          <t>3339403</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3421231</t>
+          <t>3423425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3462751</t>
+          <t>3465500</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6733180</t>
+          <t>6734137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6793684</t>
+          <t>6793449</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282533</t>
+          <t>282646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292530</t>
+          <t>292524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271242</t>
+          <t>271863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284763</t>
+          <t>284561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560282</t>
+          <t>560430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575129</t>
+          <t>575864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485613</t>
+          <t>484686</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497479</t>
+          <t>498228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508288</t>
+          <t>508988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519992</t>
+          <t>520075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999248</t>
+          <t>999053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015560</t>
+          <t>1015712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304468</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314898</t>
+          <t>314849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323767</t>
+          <t>323739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333508</t>
+          <t>333513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631508</t>
+          <t>632381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646502</t>
+          <t>646566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>29871</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>352615</t>
+          <t>353582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365143</t>
+          <t>365599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>368300</t>
+          <t>367441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382648</t>
+          <t>382318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727030</t>
+          <t>727376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745184</t>
+          <t>745952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201520</t>
+          <t>201181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210272</t>
+          <t>210279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>204650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216307</t>
+          <t>215547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412535</t>
+          <t>410963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425194</t>
+          <t>424797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254419</t>
+          <t>253652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262198</t>
+          <t>262183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265744</t>
+          <t>265411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272246</t>
+          <t>272242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523831</t>
+          <t>523311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533615</t>
+          <t>533552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>33585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>624293</t>
+          <t>622973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643675</t>
+          <t>643787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660450</t>
+          <t>661182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680320</t>
+          <t>679911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1289712</t>
+          <t>1291728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1318827</t>
+          <t>1318353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>18737</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>41468</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760270</t>
+          <t>759846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773733</t>
+          <t>773186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>796357</t>
+          <t>796541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>814789</t>
+          <t>815015</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1564197</t>
+          <t>1563282</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586239</t>
+          <t>1584865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53948</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>86710</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>102289</t>
+          <t>101231</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124314</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177422</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3306367</t>
+          <t>3307640</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3340402</t>
+          <t>3341136</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3442253</t>
+          <t>3443311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3481115</t>
+          <t>3480706</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6761470</t>
+          <t>6761643</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6814578</t>
+          <t>6812875</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306203</t>
+          <t>305817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273808</t>
+          <t>274350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286338</t>
+          <t>286693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584212</t>
+          <t>584817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597327</t>
+          <t>597356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499701</t>
+          <t>499934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514596</t>
+          <t>514543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495913</t>
+          <t>496358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506915</t>
+          <t>506926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002759</t>
+          <t>1002555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019329</t>
+          <t>1018621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291117</t>
+          <t>291922</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306706</t>
+          <t>306383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323431</t>
+          <t>324789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337461</t>
+          <t>337581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620014</t>
+          <t>620821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641228</t>
+          <t>640967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300216</t>
+          <t>301032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312240</t>
+          <t>312387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464117</t>
+          <t>463951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473231</t>
+          <t>473368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771069</t>
+          <t>771051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783973</t>
+          <t>784192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174642</t>
+          <t>173464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200303</t>
+          <t>200664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206160</t>
+          <t>206031</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377128</t>
+          <t>376924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384129</t>
+          <t>383724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32722</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249876</t>
+          <t>250772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262015</t>
+          <t>262300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238390</t>
+          <t>238251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249736</t>
+          <t>249462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493970</t>
+          <t>492659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509432</t>
+          <t>509612</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>62545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91969</t>
+          <t>91967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581954</t>
+          <t>580243</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605635</t>
+          <t>605131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>787998</t>
+          <t>786720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828574</t>
+          <t>830488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381575</t>
+          <t>1381577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1428092</t>
+          <t>1428811</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>34378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>913802</t>
+          <t>912096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927324</t>
+          <t>927331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>682346</t>
+          <t>680473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709899</t>
+          <t>709909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1603827</t>
+          <t>1605101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1634840</t>
+          <t>1635344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>88403</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136558</t>
+          <t>136067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>157336</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>219395</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3360692</t>
+          <t>3361212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3401441</t>
+          <t>3404325</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3521144</t>
+          <t>3521635</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3569299</t>
+          <t>3566672</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6896637</t>
+          <t>6899468</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6958696</t>
+          <t>6961594</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A04-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267985</t>
+          <t>267431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246680</t>
+          <t>246795</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257721</t>
+          <t>257789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517848</t>
+          <t>519389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529851</t>
+          <t>530705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479589</t>
+          <t>480462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490947</t>
+          <t>490959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479470</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494428</t>
+          <t>495134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965172</t>
+          <t>966237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983403</t>
+          <t>983962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313467</t>
+          <t>313613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327501</t>
+          <t>327157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334490</t>
+          <t>334486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645542</t>
+          <t>644631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653313</t>
+          <t>653281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>20340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>28879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345389</t>
+          <t>345957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351539</t>
+          <t>351116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364872</t>
+          <t>364884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702356</t>
+          <t>701248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719064</t>
+          <t>718411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>197913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196612</t>
+          <t>195790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205758</t>
+          <t>205730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397393</t>
+          <t>399223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408187</t>
+          <t>408853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262164</t>
+          <t>261055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269804</t>
+          <t>269837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262992</t>
+          <t>263314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275720</t>
+          <t>274969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530803</t>
+          <t>529340</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543705</t>
+          <t>543325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26907</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595404</t>
+          <t>595644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609477</t>
+          <t>609515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624949</t>
+          <t>626538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636132</t>
+          <t>636279</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1226339</t>
+          <t>1227063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1243372</t>
+          <t>1243397</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30661</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>63152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702680</t>
+          <t>702159</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723510</t>
+          <t>723357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>752850</t>
+          <t>754782</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>772127</t>
+          <t>772536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462458</t>
+          <t>1463136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490590</t>
+          <t>1490944</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45808</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>76703</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93543</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112708</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155307</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3200466</t>
+          <t>3198822</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3230214</t>
+          <t>3229717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3285654</t>
+          <t>3285484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3319925</t>
+          <t>3321668</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6499415</t>
+          <t>6495438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6542531</t>
+          <t>6542014</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>26364</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51547</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263160</t>
+          <t>263116</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281120</t>
+          <t>280779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251024</t>
+          <t>250480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269058</t>
+          <t>269076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520041</t>
+          <t>519612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546687</t>
+          <t>545224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484689</t>
+          <t>484756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500504</t>
+          <t>500678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508193</t>
+          <t>507980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519598</t>
+          <t>519581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998478</t>
+          <t>999330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017746</t>
+          <t>1017995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312902</t>
+          <t>313373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322096</t>
+          <t>322101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325733</t>
+          <t>326206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337134</t>
+          <t>337142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644320</t>
+          <t>643746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657380</t>
+          <t>657168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351988</t>
+          <t>351183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368386</t>
+          <t>368293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367120</t>
+          <t>367259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382249</t>
+          <t>382277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726527</t>
+          <t>725351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747517</t>
+          <t>747111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191321</t>
+          <t>191036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207752</t>
+          <t>207593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198739</t>
+          <t>199886</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212936</t>
+          <t>213513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397640</t>
+          <t>397410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>418668</t>
+          <t>417991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,47 +5786,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11899</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11099</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264373</t>
+          <t>265201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273026</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,49 +5899,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>275367</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>267241</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>278161</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,74%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>275367</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>268041</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>278182</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>522</t>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537013</t>
+          <t>537810</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>550211</t>
+          <t>550202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36124</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>642404</t>
+          <t>641454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655654</t>
+          <t>655975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671448</t>
+          <t>670981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>686909</t>
+          <t>686870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318326</t>
+          <t>1318318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339493</t>
+          <t>1339100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20173</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43626</t>
+          <t>43270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>40078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74260</t>
+          <t>76425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>733346</t>
+          <t>733702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>756799</t>
+          <t>756714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>781604</t>
+          <t>781442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>804574</t>
+          <t>803999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1524232</t>
+          <t>1522067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1556595</t>
+          <t>1555087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>77743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118937</t>
+          <t>121968</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>80717</t>
+          <t>83879</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>122792</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168871</t>
+          <t>168997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>228183</t>
+          <t>230362</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3297166</t>
+          <t>3294135</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3339403</t>
+          <t>3338360</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3423425</t>
+          <t>3421601</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3465500</t>
+          <t>3462338</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6734137</t>
+          <t>6731958</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282646</t>
+          <t>283370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292524</t>
+          <t>292534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271863</t>
+          <t>271184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284561</t>
+          <t>284735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560430</t>
+          <t>559487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575864</t>
+          <t>574999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484686</t>
+          <t>485534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498228</t>
+          <t>498279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508988</t>
+          <t>508930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520075</t>
+          <t>520122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999053</t>
+          <t>999674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015712</t>
+          <t>1016078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22493</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>304325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314849</t>
+          <t>315616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323739</t>
+          <t>322992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333513</t>
+          <t>333483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632381</t>
+          <t>631688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646566</t>
+          <t>646480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29871</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353582</t>
+          <t>352315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365599</t>
+          <t>365829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367441</t>
+          <t>368521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>382318</t>
+          <t>382474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727376</t>
+          <t>726728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745952</t>
+          <t>745496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201181</t>
+          <t>201155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210279</t>
+          <t>210275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204650</t>
+          <t>204522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215547</t>
+          <t>216353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410963</t>
+          <t>411296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424797</t>
+          <t>425194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253652</t>
+          <t>253984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262183</t>
+          <t>262164</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265411</t>
+          <t>264884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272242</t>
+          <t>272251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523311</t>
+          <t>524319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533552</t>
+          <t>533548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>33429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>54664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622973</t>
+          <t>623129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643787</t>
+          <t>643521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661182</t>
+          <t>660849</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679911</t>
+          <t>680117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1291728</t>
+          <t>1293188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1318353</t>
+          <t>1319220</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>40425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>759846</t>
+          <t>759723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773186</t>
+          <t>773603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>796541</t>
+          <t>797383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815015</t>
+          <t>815179</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1563282</t>
+          <t>1564325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1584865</t>
+          <t>1585113</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53214</t>
+          <t>54463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>63356</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>101231</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126017</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3307640</t>
+          <t>3305763</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3341136</t>
+          <t>3339887</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3443311</t>
+          <t>3443174</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3480706</t>
+          <t>3481186</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6761643</t>
+          <t>6759399</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6812875</t>
+          <t>6812156</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>795</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>310560</t>
+          <t>318050</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305817</t>
+          <t>314445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>282863</t>
+          <t>307502</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274350</t>
+          <t>299499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286693</t>
+          <t>311884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>593422</t>
+          <t>625552</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584817</t>
+          <t>617641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597356</t>
+          <t>629877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17367</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>509311</t>
+          <t>521598</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499934</t>
+          <t>513215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514543</t>
+          <t>526880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>502529</t>
+          <t>533880</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496358</t>
+          <t>527552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506926</t>
+          <t>538618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1011840</t>
+          <t>1055478</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002555</t>
+          <t>1044087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018621</t>
+          <t>1062173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24339</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43867</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>300503</t>
+          <t>301324</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291922</t>
+          <t>293210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306383</t>
+          <t>307599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>332051</t>
+          <t>338563</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324789</t>
+          <t>330825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337581</t>
+          <t>344151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>632554</t>
+          <t>639888</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620821</t>
+          <t>629234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640967</t>
+          <t>648661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309716</t>
+          <t>368323</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301032</t>
+          <t>358101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312387</t>
+          <t>371663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>469938</t>
+          <t>414321</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463951</t>
+          <t>404834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473368</t>
+          <t>418333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>779654</t>
+          <t>782644</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>771051</t>
+          <t>770637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>784192</t>
+          <t>788540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177383</t>
+          <t>204196</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173464</t>
+          <t>200272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>203847</t>
+          <t>222200</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>218775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206031</t>
+          <t>224711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>381230</t>
+          <t>426395</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376924</t>
+          <t>421851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383724</t>
+          <t>429024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,17 +12447,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,22 +12482,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34033</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>257518</t>
+          <t>258829</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250772</t>
+          <t>251823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262300</t>
+          <t>263539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,17 +12560,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>245189</t>
+          <t>251552</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238251</t>
+          <t>244352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249462</t>
+          <t>256003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,27 +12595,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>502707</t>
+          <t>510381</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492659</t>
+          <t>501170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509612</t>
+          <t>517137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>49130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>67419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71749</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44733</t>
+          <t>72520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91967</t>
+          <t>108152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>595239</t>
+          <t>685125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580243</t>
+          <t>670557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605131</t>
+          <t>696942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>806556</t>
+          <t>717837</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>786720</t>
+          <t>704638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>830488</t>
+          <t>729713</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1401795</t>
+          <t>1402962</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381577</t>
+          <t>1383592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1428811</t>
+          <t>1419224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34378</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>922907</t>
+          <t>791687</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>912096</t>
+          <t>781777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927331</t>
+          <t>796206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>703072</t>
+          <t>822316</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>680473</t>
+          <t>816571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709909</t>
+          <t>825989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1625981</t>
+          <t>1614003</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1605101</t>
+          <t>1603889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635344</t>
+          <t>1619652</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97118</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136067</t>
+          <t>144065</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154438</t>
+          <t>182214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>216564</t>
+          <t>236764</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3383136</t>
+          <t>3449132</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3361212</t>
+          <t>3426767</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3404325</t>
+          <t>3467193</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3546045</t>
+          <t>3608171</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3521635</t>
+          <t>3588248</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3566672</t>
+          <t>3627002</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6929180</t>
+          <t>7057303</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6899468</t>
+          <t>7026829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6961594</t>
+          <t>7081379</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
